--- a/09-Servicos-e-Custos/TCO-local-vs-OpenAI.xlsx
+++ b/09-Servicos-e-Custos/TCO-local-vs-OpenAI.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,7 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -697,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1099,7 +1100,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sobretaxa contexto longo</t>
+          <t>Sobretaxa contexto longo — entrada</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1112,7 +1113,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fator editável para contextos acima do limite de preço-base</t>
+          <t>Fator sobre o preço de input acima do limite de preço-base (1 = sem sobretaxa)</t>
         </is>
       </c>
     </row>
@@ -1133,6 +1134,46 @@
       <c r="D22" t="inlineStr">
         <is>
           <t>Preencher quando aplicável; não presumir custo zero sem confirmação</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sobretaxa contexto longo — cached</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>fator</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Fator sobre o preço de cached input (1 = sem sobretaxa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sobretaxa contexto longo — saída</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>fator</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fator sobre o preço de output (1 = sem sobretaxa)</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1157,6 +1198,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1190,6 +1232,11 @@
           <t>Custo mensal BRL</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Custo mensal BRL (Batch)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1207,13 +1254,17 @@
         <v>20</v>
       </c>
       <c r="E2" s="2">
-        <f>((Premissas!$B$14*B2)+(Premissas!$B$15*(C2+Premissas!$B$22))+(Premissas!$B$16*D2))*Premissas!$B$21</f>
+        <f>(Premissas!$B$14*B2*Premissas!$B$21)+(Premissas!$B$15*(C2+Premissas!$B$22)*Premissas!$B$23)+(Premissas!$B$16*D2*Premissas!$B$24)</f>
         <v/>
       </c>
       <c r="F2" s="2">
         <f>E2*Premissas!$B$2</f>
         <v/>
       </c>
+      <c r="G2" s="2">
+        <f>F2*Premissas!$B$20</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1231,13 +1282,17 @@
         <v>12</v>
       </c>
       <c r="E3" s="2">
-        <f>((Premissas!$B$14*B3)+(Premissas!$B$15*(C3+Premissas!$B$22))+(Premissas!$B$16*D3))*Premissas!$B$21</f>
+        <f>(Premissas!$B$14*B3*Premissas!$B$21)+(Premissas!$B$15*(C3+Premissas!$B$22)*Premissas!$B$23)+(Premissas!$B$16*D3*Premissas!$B$24)</f>
         <v/>
       </c>
       <c r="F3" s="2">
         <f>E3*Premissas!$B$2</f>
         <v/>
       </c>
+      <c r="G3" s="2">
+        <f>F3*Premissas!$B$20</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1255,11 +1310,15 @@
         <v>1.2</v>
       </c>
       <c r="E4" s="2">
-        <f>((Premissas!$B$14*B4)+(Premissas!$B$15*(C4+Premissas!$B$22))+(Premissas!$B$16*D4))*Premissas!$B$21</f>
+        <f>(Premissas!$B$14*B4*Premissas!$B$21)+(Premissas!$B$15*(C4+Premissas!$B$22)*Premissas!$B$23)+(Premissas!$B$16*D4*Premissas!$B$24)</f>
         <v/>
       </c>
       <c r="F4" s="2">
         <f>E4*Premissas!$B$2</f>
+        <v/>
+      </c>
+      <c r="G4" s="2">
+        <f>F4*Premissas!$B$20</f>
         <v/>
       </c>
     </row>
@@ -1308,11 +1367,11 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CAPEX / vida útil</t>
+          <t>(CAPEX − valor residual) / vida útil</t>
         </is>
       </c>
       <c r="C2" s="2">
-        <f>Premissas!B3/Premissas!B4</f>
+        <f>(Premissas!B3-Premissas!B5)/Premissas!B4</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1433,6 +1492,8 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1466,6 +1527,16 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Break-even tokens M/mês (Batch)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Custo API blended BRL/M (mix atual)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
@@ -1485,11 +1556,19 @@
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>C2/(((Premissas!$B$14*API_OpenAI!B2)+(Premissas!$B$15*(API_OpenAI!C2+Premissas!$B$22))+(Premissas!$B$16*API_OpenAI!D2))*Premissas!$B$21/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <f>C2/H2</f>
         <v/>
       </c>
       <c r="F2" s="2">
         <f>IF(D2&gt;0,"Local tende a vencer no custo direto","API tende a vencer no custo direto")</f>
+        <v/>
+      </c>
+      <c r="G2" s="2">
+        <f>E2/Premissas!$B$20</f>
+        <v/>
+      </c>
+      <c r="H2" s="2">
+        <f>API_OpenAI!F2/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16)</f>
         <v/>
       </c>
     </row>
@@ -1511,11 +1590,19 @@
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>C3/(((Premissas!$B$14*API_OpenAI!B3)+(Premissas!$B$15*(API_OpenAI!C3+Premissas!$B$22))+(Premissas!$B$16*API_OpenAI!D3))*Premissas!$B$21/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <f>C3/H3</f>
         <v/>
       </c>
       <c r="F3" s="2">
         <f>IF(D3&gt;0,"Local tende a vencer no custo direto","API tende a vencer no custo direto")</f>
+        <v/>
+      </c>
+      <c r="G3" s="2">
+        <f>E3/Premissas!$B$20</f>
+        <v/>
+      </c>
+      <c r="H3" s="2">
+        <f>API_OpenAI!F3/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16)</f>
         <v/>
       </c>
     </row>
@@ -1537,11 +1624,19 @@
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>C4/(((Premissas!$B$14*API_OpenAI!B4)+(Premissas!$B$15*(API_OpenAI!C4+Premissas!$B$22))+(Premissas!$B$16*API_OpenAI!D4))*Premissas!$B$21/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <f>C4/H4</f>
         <v/>
       </c>
       <c r="F4" s="2">
         <f>IF(D4&gt;0,"Local tende a vencer no custo direto","API tende a vencer no custo direto")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2">
+        <f>E4/Premissas!$B$20</f>
+        <v/>
+      </c>
+      <c r="H4" s="2">
+        <f>API_OpenAI!F4/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16)</f>
         <v/>
       </c>
     </row>
@@ -1557,20 +1652,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Câmbio</t>
+          <t>Câmbio BRL/USD</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1591,6 +1689,21 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>TCO local BRL/mês</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Break-even Sol M/mês</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Break-even Terra M/mês</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Break-even Luna M/mês</t>
         </is>
       </c>
     </row>
@@ -1599,19 +1712,31 @@
         <v>4.4</v>
       </c>
       <c r="B2" s="2">
-        <f>(Premissas!B14*API_OpenAI!B4+Premissas!B15*API_OpenAI!C4+Premissas!B16*API_OpenAI!D4)*A2</f>
+        <f>API_OpenAI!$E$4*$A2</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>(Premissas!B14*API_OpenAI!B3+Premissas!B15*API_OpenAI!C3+Premissas!B16*API_OpenAI!D3)*A2</f>
+        <f>API_OpenAI!$E$3*$A2</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>(Premissas!B14*API_OpenAI!B2+Premissas!B15*API_OpenAI!C2+Premissas!B16*API_OpenAI!D2)*A2</f>
+        <f>API_OpenAI!$E$2*$A2</f>
         <v/>
       </c>
       <c r="E2" s="2">
-        <f>Local!C7</f>
+        <f>Local!$C$7</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>E2/(D2/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>E2/(C2/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>E2/(B2/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
         <v/>
       </c>
     </row>
@@ -1620,19 +1745,31 @@
         <v>4.95</v>
       </c>
       <c r="B3" s="2">
-        <f>(Premissas!B14*API_OpenAI!B4+Premissas!B15*API_OpenAI!C4+Premissas!B16*API_OpenAI!D4)*A3</f>
+        <f>API_OpenAI!$E$4*$A3</f>
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>(Premissas!B14*API_OpenAI!B3+Premissas!B15*API_OpenAI!C3+Premissas!B16*API_OpenAI!D3)*A3</f>
+        <f>API_OpenAI!$E$3*$A3</f>
         <v/>
       </c>
       <c r="D3" s="2">
-        <f>(Premissas!B14*API_OpenAI!B2+Premissas!B15*API_OpenAI!C2+Premissas!B16*API_OpenAI!D2)*A3</f>
+        <f>API_OpenAI!$E$2*$A3</f>
         <v/>
       </c>
       <c r="E3" s="2">
-        <f>Local!C7</f>
+        <f>Local!$C$7</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>E3/(D3/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>E3/(C3/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>E3/(B3/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
         <v/>
       </c>
     </row>
@@ -1641,19 +1778,31 @@
         <v>5.5</v>
       </c>
       <c r="B4" s="2">
-        <f>(Premissas!B14*API_OpenAI!B4+Premissas!B15*API_OpenAI!C4+Premissas!B16*API_OpenAI!D4)*A4</f>
+        <f>API_OpenAI!$E$4*$A4</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>(Premissas!B14*API_OpenAI!B3+Premissas!B15*API_OpenAI!C3+Premissas!B16*API_OpenAI!D3)*A4</f>
+        <f>API_OpenAI!$E$3*$A4</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>(Premissas!B14*API_OpenAI!B2+Premissas!B15*API_OpenAI!C2+Premissas!B16*API_OpenAI!D2)*A4</f>
+        <f>API_OpenAI!$E$2*$A4</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>Local!C7</f>
+        <f>Local!$C$7</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>E4/(D4/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>E4/(C4/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>E4/(B4/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
         <v/>
       </c>
     </row>
@@ -1662,19 +1811,31 @@
         <v>6.05</v>
       </c>
       <c r="B5" s="2">
-        <f>(Premissas!B14*API_OpenAI!B4+Premissas!B15*API_OpenAI!C4+Premissas!B16*API_OpenAI!D4)*A5</f>
+        <f>API_OpenAI!$E$4*$A5</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>(Premissas!B14*API_OpenAI!B3+Premissas!B15*API_OpenAI!C3+Premissas!B16*API_OpenAI!D3)*A5</f>
+        <f>API_OpenAI!$E$3*$A5</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>(Premissas!B14*API_OpenAI!B2+Premissas!B15*API_OpenAI!C2+Premissas!B16*API_OpenAI!D2)*A5</f>
+        <f>API_OpenAI!$E$2*$A5</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>Local!C7</f>
+        <f>Local!$C$7</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>E5/(D5/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>E5/(C5/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>E5/(B5/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
         <v/>
       </c>
     </row>
@@ -1683,19 +1844,432 @@
         <v>6.6</v>
       </c>
       <c r="B6" s="2">
-        <f>(Premissas!B14*API_OpenAI!B4+Premissas!B15*API_OpenAI!C4+Premissas!B16*API_OpenAI!D4)*A6</f>
+        <f>API_OpenAI!$E$4*$A6</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>(Premissas!B14*API_OpenAI!B3+Premissas!B15*API_OpenAI!C3+Premissas!B16*API_OpenAI!D3)*A6</f>
+        <f>API_OpenAI!$E$3*$A6</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>(Premissas!B14*API_OpenAI!B2+Premissas!B15*API_OpenAI!C2+Premissas!B16*API_OpenAI!D2)*A6</f>
+        <f>API_OpenAI!$E$2*$A6</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>Local!C7</f>
+        <f>Local!$C$7</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>E6/(D6/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>E6/(C6/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>E6/(B6/(Premissas!$B$14+Premissas!$B$15+Premissas!$B$16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Vida útil (meses)</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>CAPEX amortizado BRL/mês</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>TCO local BRL/mês</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Break-even Sol M/mês</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Break-even Terra M/mês</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Break-even Luna M/mês</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <f>(Premissas!$B$3-Premissas!$B$5)/A9</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>Local!$C$7-Local!$C$2+B9</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>C9/Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>C9/Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>C9/Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <f>(Premissas!$B$3-Premissas!$B$5)/A10</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>Local!$C$7-Local!$C$2+B10</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>C10/Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>C10/Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>C10/Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>48</v>
+      </c>
+      <c r="B11">
+        <f>(Premissas!$B$3-Premissas!$B$5)/A11</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>Local!$C$7-Local!$C$2+B11</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>C11/Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>C11/Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>C11/Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Fator utilização</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Capacidade M tokens/mês</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Custo local BRL/M tokens</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>API Sol blended BRL/M</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>API Terra blended BRL/M</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>API Luna blended BRL/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B14">
+        <f>Premissas!$B$17*3600*Premissas!$B$7*Premissas!$B$8*A14/1000000</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>Local!$C$7/B14</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B15">
+        <f>Premissas!$B$17*3600*Premissas!$B$7*Premissas!$B$8*A15/1000000</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>Local!$C$7/B15</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B16">
+        <f>Premissas!$B$17*3600*Premissas!$B$7*Premissas!$B$8*A16/1000000</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>Local!$C$7/B16</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B17">
+        <f>Premissas!$B$17*3600*Premissas!$B$7*Premissas!$B$8*A17/1000000</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>Local!$C$7/B17</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Tarifa BRL/kWh</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Energia BRL/mês</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>TCO local BRL/mês</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>Break-even Sol M/mês</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Break-even Terra M/mês</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Break-even Luna M/mês</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <f>Premissas!$B$9*0.7</f>
+        <v/>
+      </c>
+      <c r="B20">
+        <f>Premissas!$B$6*Premissas!$B$7*Premissas!$B$8*A20</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>Local!$C$7-Local!$C$3+B20</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>C20/Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>C20/Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>C20/Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <f>Premissas!$B$9*0.85</f>
+        <v/>
+      </c>
+      <c r="B21">
+        <f>Premissas!$B$6*Premissas!$B$7*Premissas!$B$8*A21</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>Local!$C$7-Local!$C$3+B21</f>
+        <v/>
+      </c>
+      <c r="D21">
+        <f>C21/Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>C21/Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>C21/Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <f>Premissas!$B$9*1</f>
+        <v/>
+      </c>
+      <c r="B22">
+        <f>Premissas!$B$6*Premissas!$B$7*Premissas!$B$8*A22</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>Local!$C$7-Local!$C$3+B22</f>
+        <v/>
+      </c>
+      <c r="D22">
+        <f>C22/Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>C22/Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F22">
+        <f>C22/Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <f>Premissas!$B$9*1.15</f>
+        <v/>
+      </c>
+      <c r="B23">
+        <f>Premissas!$B$6*Premissas!$B$7*Premissas!$B$8*A23</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>Local!$C$7-Local!$C$3+B23</f>
+        <v/>
+      </c>
+      <c r="D23">
+        <f>C23/Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E23">
+        <f>C23/Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F23">
+        <f>C23/Break_even!$H$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <f>Premissas!$B$9*1.3</f>
+        <v/>
+      </c>
+      <c r="B24">
+        <f>Premissas!$B$6*Premissas!$B$7*Premissas!$B$8*A24</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>Local!$C$7-Local!$C$3+B24</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>C24/Break_even!$H$2</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>C24/Break_even!$H$3</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>C24/Break_even!$H$4</f>
         <v/>
       </c>
     </row>
@@ -1712,7 +2286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1759,6 +2333,30 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Revisão</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-01 (rev. 2): câmbio aplicado ao break-even; valor residual no CAPEX; coluna Batch; fatores de contexto longo por categoria; sensibilidade por câmbio, vida útil, utilização e tarifa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Recalcular</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arquivo salvo sem valores em cache; abra no Excel/LibreOffice e force o recálculo antes de ler resultados.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
